--- a/data/phase1_issue_classification.xlsx
+++ b/data/phase1_issue_classification.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P127"/>
+  <dimension ref="A1:P137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="4" max="4"/>
@@ -515,30 +515,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>milvus</t>
+          <t>chroma</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47635</v>
+        <v>7375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>milvus-io/milvus</t>
+          <t>chroma-core/chroma</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[Bug]: Search fails with Code 0 immediately after Collection.load() returns success</t>
+          <t>[Bug]:  Concurrent `create_collection` + `delete_collection` on the same collection can lose the created collection (lost update)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G2" t="b">
@@ -546,46 +541,38 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-02-06T13:10:41Z</t>
+          <t>2026-07-02T00:00:00Z</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.5.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)chroma\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TP_ACK_CLOSED_NOFIX</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>0.92</v>
+          <t>D 未裁决：报告者自标，待维护者（外部 PR #7643 已挂未合并；社区机制分析存在）</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -595,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47636</v>
+        <v>47635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -604,7 +591,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[Bug]: Expr parser returns code=0 (Success) and leaks internal lexer errors</t>
+          <t>[Bug]: Search fails with Code 0 immediately after Collection.load() returns success</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -622,7 +609,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-02-06T13:22:08Z</t>
+          <t>2026-02-06T13:10:41Z</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -637,26 +624,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>STALE_NO_FIX</t>
+          <t>TP_ACK_CLOSED_NOFIX</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>D 未裁决：过期未修</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -665,7 +658,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47729</v>
+        <v>47636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -674,17 +667,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[Bug]: Index parameter nprobe validation missing - accepts nprobe=0</t>
+          <t>[Bug]: Expr parser returns code=0 (Success) and leaks internal lexer errors</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>reopened</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="G4" t="b">
@@ -692,12 +685,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-02-10T12:43:49Z</t>
+          <t>2026-02-06T13:22:08Z</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.6.10</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -707,31 +700,23 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>STALE_NO_FIX</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：过期未修</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -741,7 +726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47752</v>
+        <v>47729</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -750,17 +735,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[Bug]: Index parameter ef validation missing - accepts ef=0</t>
+          <t>[Bug]: Index parameter nprobe validation missing - accepts nprobe=0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="G5" t="b">
@@ -768,7 +753,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-02-11T13:56:28Z</t>
+          <t>2026-02-10T12:43:49Z</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -783,7 +768,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TP_ACK_CLOSED_NOFIX</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -798,7 +783,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
+          <t>B 真 bug：维护者确认但未修(open)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -817,7 +802,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47755</v>
+        <v>47752</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -826,7 +811,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[Bug]: Filter expression validation too lenient</t>
+          <t>[Bug]: Index parameter ef validation missing - accepts ef=0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -844,7 +829,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-02-11T14:26:40Z</t>
+          <t>2026-02-11T13:56:28Z</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -893,7 +878,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47763</v>
+        <v>47755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -902,7 +887,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[Bug]:  Field name validation missing - accepts invalid field names causing data inaccessibility</t>
+          <t>[Bug]: Filter expression validation too lenient</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -920,7 +905,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-02-12T09:44:39Z</t>
+          <t>2026-02-11T14:26:40Z</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -935,12 +920,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_ACK_CLOSED_NOFIX</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -950,7 +935,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -969,7 +954,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47766</v>
+        <v>47763</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -978,7 +963,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[Bug]: Data type validation missing - accepts integer into string field</t>
+          <t>[Bug]:  Field name validation missing - accepts invalid field names causing data inaccessibility</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -996,7 +981,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-02-13T00:49:32Z</t>
+          <t>2026-02-12T09:44:39Z</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1026,7 +1011,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
+          <t>改判 2026-09-05:原标 TP_FIXED_PR 系错账——关联修复 PR 未 merge(closed-unmerged),用户确认知情范围内未修复;TP_ACK_CLOSED_NOFIX</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1045,7 +1030,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47767</v>
+        <v>47766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1054,7 +1039,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[Bug]: Empty query vector accepted in search - no validation error</t>
+          <t>[Bug]: Data type validation missing - accepts integer into string field</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1072,7 +1057,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-02-13T01:47:48Z</t>
+          <t>2026-02-13T00:49:32Z</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1087,31 +1072,31 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>TP_ACK_CLOSED_NOFIX</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
+          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="10">
@@ -1121,7 +1106,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47785</v>
+        <v>47767</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1130,7 +1115,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fix: add nprobe parameter validation for IVF index search</t>
+          <t>[Bug]: Empty query vector accepted in search - no validation error</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1138,46 +1123,57 @@
           <t>closed</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="G10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-02-17T16:34:27Z</t>
+          <t>2026-02-13T01:47:48Z</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.6.11</t>
+          <t>2.6.10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>releases-api (latest &lt;= created_at)</t>
+          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SELF_PR_CLOSED</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EXCLUDED</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>排除：自提 PR(非 issue)</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+          <t>C 误报：by-design(无 bug)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1186,7 +1182,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49059</v>
+        <v>47785</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1195,7 +1191,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[Bug]: COSINE Metric Returns Distance &gt; 1.0 for Identical Vectors (Precision Overflow)</t>
+          <t>fix: add nprobe parameter validation for IVF index search</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1203,56 +1199,43 @@
           <t>closed</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-15T13:35:04Z</t>
+          <t>2026-02-17T16:34:27Z</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.6.12</t>
+          <t>2.6.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>releases-api (latest &lt;= created_at)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>TP_ACK_CLOSED_NOFIX</t>
+          <t>SELF_PR_CLOSED</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>EXCLUDED</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>0.95</v>
+          <t>排除：自提 PR(非 issue)</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1262,7 +1245,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49823</v>
+        <v>49059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1271,12 +1254,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 accepts nprobe=0 in search requests without validation</t>
+          <t>[Bug]: COSINE Metric Returns Distance &gt; 1.0 for Identical Vectors (Precision Overflow)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G12" t="b">
@@ -1284,12 +1272,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-05-15T06:44:57Z</t>
+          <t>2026-04-15T13:35:04Z</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.6.16</t>
+          <t>2.6.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1299,7 +1287,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>TP_ACK_CLOSED_NOFIX</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1314,7 +1302,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
+          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1333,7 +1321,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49824</v>
+        <v>49823</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1342,17 +1330,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 returns success when creating a collection with a duplicate name</t>
+          <t>[Bug]: REST API v2 accepts nprobe=0 in search requests without validation</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G13" t="b">
@@ -1360,7 +1343,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-05-15T06:45:26Z</t>
+          <t>2026-05-15T06:44:57Z</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1375,26 +1358,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+          <t>B 真 bug：维护者确认但未修(open)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1403,7 +1392,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49843</v>
+        <v>49824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1412,7 +1401,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 silently drops negative collection.ttl.seconds on collection create</t>
+          <t>[Bug]: REST API v2 returns success when creating a collection with a duplicate name</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1430,7 +1419,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-15T13:28:01Z</t>
+          <t>2026-05-15T06:45:26Z</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1445,31 +1434,23 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1479,7 +1460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49844</v>
+        <v>49843</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1488,7 +1469,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 query accepts null/missing filter and silently returns all entities</t>
+          <t>[Bug]: REST API v2 silently drops negative collection.ttl.seconds on collection create</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1506,7 +1487,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-15T16:07:17Z</t>
+          <t>2026-05-15T13:28:01Z</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1516,27 +1497,27 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>releases-api (latest &lt;= created_at)</t>
+          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1555,7 +1536,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49849</v>
+        <v>49844</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1564,7 +1545,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 insert returns insertCount=1 for duplicate primary key (upsert semantics)</t>
+          <t>[Bug]: REST API v2 query accepts null/missing filter and silently returns all entities</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1582,7 +1563,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-05-16T02:40:01Z</t>
+          <t>2026-05-15T16:07:17Z</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1597,26 +1578,32 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+          <t>C 误报：维护者判定 by-design</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1625,7 +1612,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49850</v>
+        <v>49849</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1634,7 +1621,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 describe indexes requires indexName, cannot list all indexes</t>
+          <t>[Bug]: REST API v2 insert returns insertCount=1 for duplicate primary key (upsert semantics)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1652,7 +1639,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-16T02:40:11Z</t>
+          <t>2026-05-16T02:40:01Z</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1685,8 +1672,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1695,7 +1680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49889</v>
+        <v>49850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1704,12 +1689,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 accepts empty string for `dbName` parameter</t>
+          <t>[Bug]: REST API v2 describe indexes requires indexName, cannot list all indexes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G18" t="b">
@@ -1717,7 +1707,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-18T16:25:43Z</t>
+          <t>2026-05-16T02:40:11Z</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1727,36 +1717,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>releases-api (latest &lt;= created_at)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>0.85</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1766,7 +1748,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>49890</v>
+        <v>49889</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1775,17 +1757,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 accepts non-integer `Request-Timeout` header values</t>
+          <t>[Bug]: REST API v2 accepts empty string for `dbName` parameter</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G19" t="b">
@@ -1793,7 +1770,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-18T16:26:03Z</t>
+          <t>2026-05-18T16:25:43Z</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1808,12 +1785,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1823,7 +1800,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：维护者确认但未修(open)</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1832,7 +1809,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20">
@@ -1842,7 +1819,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>49928</v>
+        <v>49890</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1851,7 +1828,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[Bug]: Default proxy.maxDimension=32768 is too permissive, potential DoS risk via high-dimensional collection creation</t>
+          <t>[Bug]: REST API v2 accepts non-integer `Request-Timeout` header values</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1869,7 +1846,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-19T14:55:15Z</t>
+          <t>2026-05-18T16:26:03Z</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1884,31 +1861,31 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="21">
@@ -1918,7 +1895,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>49929</v>
+        <v>49928</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1927,7 +1904,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[Bug]: REST API and PyMilvus SDK have inconsistent default index creation behavior</t>
+          <t>[Bug]: Default proxy.maxDimension=32768 is too permissive, potential DoS risk via high-dimensional collection creation</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1945,7 +1922,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-19T14:56:12Z</t>
+          <t>2026-05-19T14:55:15Z</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1994,7 +1971,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49930</v>
+        <v>49929</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2003,12 +1980,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 accepts invalid searchParams (ef=0/-1 for HNSW, nprobe=0/-1 for IVF_FLAT) without validation</t>
+          <t>[Bug]: REST API and PyMilvus SDK have inconsistent default index creation behavior</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G22" t="b">
@@ -2016,7 +1998,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-19T15:23:18Z</t>
+          <t>2026-05-19T14:56:12Z</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2031,31 +2013,31 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
+          <t>C 误报：by-design(无 bug)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="23">
@@ -2065,7 +2047,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50018</v>
+        <v>49930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2074,17 +2056,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 aliases/list accepts empty collectionName while other endpoints properly reject it</t>
+          <t>[Bug]: REST API v2 accepts invalid searchParams (ef=0/-1 for HNSW, nprobe=0/-1 for IVF_FLAT) without validation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -2092,7 +2069,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-05-23T06:03:05Z</t>
+          <t>2026-05-19T15:23:18Z</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2107,7 +2084,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>TP_ACK_CLOSED_NOFIX</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2122,16 +2099,16 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
+          <t>B 真 bug：维护者确认但未修(open)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="24">
@@ -2141,7 +2118,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50192</v>
+        <v>50018</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2150,12 +2127,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[Bug] Concurrent rename and create with same target name both succeed, causing state violation</t>
+          <t>[Bug]: REST API v2 aliases/list accepts empty collectionName while other endpoints properly reject it</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G24" t="b">
@@ -2163,7 +2145,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-05-30T06:37:27Z</t>
+          <t>2026-05-23T06:03:05Z</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2178,31 +2160,31 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>TP_ACK_CLOSED_NOFIX</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>B 真 bug：维护者确认但未修(closed nofix)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>FALSE_POSITIVE</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>C 误报：by-design(无 bug)</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
       <c r="P24" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="25">
@@ -2212,7 +2194,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>50193</v>
+        <v>50192</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -2221,7 +2203,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[Bug] get_stats returns rowCount=0 after successful insert and load (v2.6.16, regression from #30663)</t>
+          <t>[Bug] Concurrent rename and create with same target name both succeed, causing state violation</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2234,7 +2216,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-30T06:37:53Z</t>
+          <t>2026-05-30T06:37:27Z</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2283,7 +2265,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50194</v>
+        <v>50193</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2292,7 +2274,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[Bug] Concurrent delete and search returns stale/deleted data</t>
+          <t>[Bug] get_stats returns rowCount=0 after successful insert and load (v2.6.16, regression from #30663)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2305,7 +2287,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-30T06:38:28Z</t>
+          <t>2026-05-30T06:37:53Z</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2354,7 +2336,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50305</v>
+        <v>50194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -2363,17 +2345,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[Bug] Search on unloaded collection returns valid results (code=0)</t>
+          <t>[Bug] Concurrent delete and search returns stale/deleted data</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G27" t="b">
@@ -2381,41 +2358,47 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:34Z</t>
+          <t>2026-05-30T06:38:28Z</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.6.17</t>
+          <t>2.6.16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>releases-api (latest &lt;= created_at)</t>
+          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+          <t>C 误报：by-design(无 bug)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2424,7 +2407,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50306</v>
+        <v>50305</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -2433,7 +2416,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[Bug] Duplicate collection creation returns code=0 instead of error</t>
+          <t>[Bug] Search on unloaded collection returns valid results (code=0)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2451,7 +2434,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:35Z</t>
+          <t>2026-06-05T03:00:34Z</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2484,8 +2467,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2494,7 +2475,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>50307</v>
+        <v>50306</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2503,7 +2484,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[Bug] Drop non-existent collection returns code=0 instead of code=4</t>
+          <t>[Bug] Duplicate collection creation returns code=0 instead of error</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2521,7 +2502,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:36Z</t>
+          <t>2026-06-05T03:00:35Z</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2554,8 +2535,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2564,7 +2543,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>50308</v>
+        <v>50307</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -2573,7 +2552,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[Bug] Delete accepts both filter and ids (mutually exclusive) silently</t>
+          <t>[Bug] Drop non-existent collection returns code=0 instead of code=4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2591,7 +2570,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:37Z</t>
+          <t>2026-06-05T03:00:36Z</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2624,8 +2603,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2634,7 +2611,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>50309</v>
+        <v>50308</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -2643,7 +2620,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[Bug] Consistency level silently accepts invalid values and defaults to Bounded</t>
+          <t>[Bug] Delete accepts both filter and ids (mutually exclusive) silently</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2661,7 +2638,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:39Z</t>
+          <t>2026-06-05T03:00:37Z</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2694,8 +2671,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2704,7 +2679,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>50310</v>
+        <v>50309</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2713,7 +2688,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[Bug] REST API: Insert accepts 101 entities (exceeding documented 100 limit)</t>
+          <t>[Bug] Consistency level silently accepts invalid values and defaults to Bounded</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2731,7 +2706,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:40Z</t>
+          <t>2026-06-05T03:00:39Z</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2764,8 +2739,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2774,7 +2747,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>50311</v>
+        <v>50310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2783,7 +2756,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[Bug] REST API: Unicode-only collection names silently accepted</t>
+          <t>[Bug] REST API: Insert accepts 101 entities (exceeding documented 100 limit)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2801,7 +2774,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:41Z</t>
+          <t>2026-06-05T03:00:40Z</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2834,8 +2807,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2844,7 +2815,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>50312</v>
+        <v>50311</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2853,7 +2824,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[Bug] Rename collection to its own name returns code=0</t>
+          <t>[Bug] REST API: Unicode-only collection names silently accepted</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2871,7 +2842,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-06-05T03:00:42Z</t>
+          <t>2026-06-05T03:00:41Z</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2904,8 +2875,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2914,7 +2883,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>50313</v>
+        <v>50312</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2923,7 +2892,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[Bug] Search on unloaded collection returns valid results (code=0)</t>
+          <t>[Bug] Rename collection to its own name returns code=0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2941,7 +2910,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-06-05T03:17:32Z</t>
+          <t>2026-06-05T03:00:42Z</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2951,7 +2920,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>releases-api (latest &lt;= created_at)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2974,8 +2943,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2984,7 +2951,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>50314</v>
+        <v>50313</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2993,7 +2960,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[Bug] Duplicate collection creation returns code=0 instead of error</t>
+          <t>[Bug] Search on unloaded collection returns valid results (code=0)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3011,7 +2978,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-06-05T03:17:34Z</t>
+          <t>2026-06-05T03:17:32Z</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3044,8 +3011,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3054,7 +3019,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>50315</v>
+        <v>50314</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3063,7 +3028,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[Bug] Drop non-existent collection returns code=0 instead of code=4</t>
+          <t>[Bug] Duplicate collection creation returns code=0 instead of error</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3114,8 +3079,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3124,7 +3087,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>50316</v>
+        <v>50315</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -3133,7 +3096,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[Bug] Delete endpoint accepts both filter and ids (mutually exclusive) silently</t>
+          <t>[Bug] Drop non-existent collection returns code=0 instead of code=4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3151,7 +3114,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-06-05T03:17:35Z</t>
+          <t>2026-06-05T03:17:34Z</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3184,8 +3147,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3194,7 +3155,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>50317</v>
+        <v>50316</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -3203,7 +3164,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[Bug] REST API: Insert accepts 101 entities (exceeding documented 100 limit)</t>
+          <t>[Bug] Delete endpoint accepts both filter and ids (mutually exclusive) silently</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3221,7 +3182,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-06-05T03:17:37Z</t>
+          <t>2026-06-05T03:17:35Z</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3254,8 +3215,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3264,7 +3223,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>50318</v>
+        <v>50317</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -3273,7 +3232,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[Bug] Collection names with leading underscore accepted despite naming rules</t>
+          <t>[Bug] REST API: Insert accepts 101 entities (exceeding documented 100 limit)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3291,7 +3250,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-05T03:17:38Z</t>
+          <t>2026-06-05T03:17:37Z</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3324,8 +3283,6 @@
           <t>D 未裁决：报告者自行关闭</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3334,7 +3291,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>50319</v>
+        <v>50318</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -3343,12 +3300,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[Bug]: Search on unloaded collection returns valid results (code=0)</t>
+          <t>[Bug] Collection names with leading underscore accepted despite naming rules</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G41" t="b">
@@ -3356,7 +3318,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-05T03:23:48Z</t>
+          <t>2026-06-05T03:17:38Z</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3371,31 +3333,23 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3405,7 +3359,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>50321</v>
+        <v>50319</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -3414,7 +3368,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[Bug]: Duplicate collection creation returns code=0 instead of error</t>
+          <t>[Bug]: Search on unloaded collection returns valid results (code=0)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3427,7 +3381,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-05T03:25:16Z</t>
+          <t>2026-06-05T03:23:48Z</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3462,7 +3416,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3476,7 +3430,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>50322</v>
+        <v>50321</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -3485,7 +3439,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[Bug]: Drop non-existent collection returns code=0 instead of code=4</t>
+          <t>[Bug]: Duplicate collection creation returns code=0 instead of error</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3498,7 +3452,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-05T03:26:34Z</t>
+          <t>2026-06-05T03:25:16Z</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3537,7 +3491,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="44">
@@ -3547,7 +3501,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>50323</v>
+        <v>50322</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -3556,7 +3510,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[Bug]: Delete endpoint accepts both filter and ids (mutually exclusive) silently</t>
+          <t>[Bug]: Drop non-existent collection returns code=0 instead of code=4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3569,7 +3523,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-05T03:28:00Z</t>
+          <t>2026-06-05T03:26:34Z</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3584,31 +3538,31 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
+          <t>C 误报：by-design(无 bug)</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="45">
@@ -3618,7 +3572,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>50324</v>
+        <v>50323</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -3627,17 +3581,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[Bug]: REST API: Insert accepts 101 entities (exceeding documented 100 limit)</t>
+          <t>[Bug]: Delete endpoint accepts both filter and ids (mutually exclusive) silently</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G45" t="b">
@@ -3645,7 +3594,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-05T03:29:10Z</t>
+          <t>2026-06-05T03:28:00Z</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3660,27 +3609,27 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
+          <t>B 真 bug：维护者确认但未修(open)</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3694,7 +3643,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>50325</v>
+        <v>50324</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3703,7 +3652,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[Bug]: Collection names with leading underscore accepted despite naming rules</t>
+          <t>[Bug]: REST API: Insert accepts 101 entities (exceeding documented 100 limit)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3721,7 +3670,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-06-05T03:30:12Z</t>
+          <t>2026-06-05T03:29:10Z</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3736,7 +3685,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3751,7 +3700,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
+          <t>C 误报：维护者判定 by-design</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3760,7 +3709,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="47">
@@ -3770,7 +3719,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>50351</v>
+        <v>50325</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3779,7 +3728,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2: shardsNum=0/-1/65535 accepted with HTTP 200 + code=200</t>
+          <t>[Bug]: Collection names with leading underscore accepted despite naming rules</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3797,7 +3746,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-06-07T04:01:01Z</t>
+          <t>2026-06-05T03:30:12Z</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3832,11 +3781,11 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="48">
@@ -3846,7 +3795,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>50352</v>
+        <v>50351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -3855,7 +3804,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2: metricType="" and consistencyLevel="None" silently accepted on collections/create</t>
+          <t>[Bug]: REST API v2: shardsNum=0/-1/65535 accepted with HTTP 200 + code=200</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3873,7 +3822,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-06-07T04:07:24Z</t>
+          <t>2026-06-07T04:01:01Z</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3912,7 +3861,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="49">
@@ -3922,7 +3871,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>50353</v>
+        <v>50352</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3931,12 +3880,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2: search returns HTTP 200 for limit=0/-1 and dimension mismatch</t>
+          <t>[Bug]: REST API v2: metricType="" and consistencyLevel="None" silently accepted on collections/create</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G49" t="b">
@@ -3944,7 +3898,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-06-07T04:09:49Z</t>
+          <t>2026-06-07T04:07:24Z</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3959,31 +3913,31 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>C 误报：by-design(无 bug)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
       <c r="P49" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="50">
@@ -3993,7 +3947,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>50354</v>
+        <v>50353</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -4002,7 +3956,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2: password complexity not enforced — "abcdefgh" accepted on users/create</t>
+          <t>[Bug]: REST API v2: search returns HTTP 200 for limit=0/-1 and dimension mismatch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4015,7 +3969,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-06-07T04:14:07Z</t>
+          <t>2026-06-07T04:09:49Z</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4064,7 +4018,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>50355</v>
+        <v>50354</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -4073,7 +4027,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[Bug]: Upsert fails on autoID=true collections despite documentation claiming support</t>
+          <t>[Bug]: REST API v2: password complexity not enforced — "abcdefgh" accepted on users/create</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4086,7 +4040,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-06-07T04:36:14Z</t>
+          <t>2026-06-07T04:14:07Z</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4101,12 +4055,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4116,7 +4070,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：维护者确认但未修(open)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4135,7 +4089,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>51084</v>
+        <v>50355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -4144,17 +4098,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[Bug]: REST API silently substitutes invalid `consistencyLevel` enum value with default instead of rejecting</t>
+          <t>[Bug]: Upsert fails on autoID=true collections despite documentation claiming support</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G52" t="b">
@@ -4162,17 +4111,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-07-06T10:13:21Z</t>
+          <t>2026-06-07T04:36:14Z</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2.6.19</t>
+          <t>2.6.17</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>(?i)milvusdb/milvus:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4211,7 +4160,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>51085</v>
+        <v>51084</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -4220,7 +4169,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[Bug]: REST API silently substitutes invalid `vectorFieldType` enum value with default instead of rejecting</t>
+          <t>[Bug]: REST API silently substitutes invalid `consistencyLevel` enum value with default instead of rejecting</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4238,7 +4187,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-07-06T10:14:32Z</t>
+          <t>2026-07-06T10:13:21Z</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4273,7 +4222,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4287,7 +4236,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>51809</v>
+        <v>51085</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -4296,54 +4245,65 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fix: validate vector search params via knowhere Config::Load at plan creation (#47729)</t>
+          <t>[Bug]: REST API silently substitutes invalid `vectorFieldType` enum value with default instead of rejecting</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-07-24T05:37:48Z</t>
+          <t>2026-07-06T10:14:32Z</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2.6.20</t>
+          <t>2.6.19</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>releases-api (latest &lt;= created_at)</t>
+          <t>(?i)milvusdb/milvus:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>SELF_PR_OPEN</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>EXCLUDED</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>排除：自提 PR(非 issue)</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4352,7 +4312,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52307</v>
+        <v>51809</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -4361,64 +4321,51 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[Bug]: entities/upsert JSON field — plain string overwrites valid JSON; written value unreadable via gRPC; REST/gRPC store inconsistent formats</t>
+          <t>fix: validate vector search params via knowhere Config::Load at plan creation (#47729)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-07T13:09:40Z</t>
+          <t>2026-07-24T05:37:48Z</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3.0.0</t>
+          <t>2.6.20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>releases-api (latest &lt;= created_at)</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>SELF_PR_OPEN</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>EXCLUDED</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>0.95</v>
+          <t>排除：自提 PR(非 issue)</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4428,7 +4375,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52308</v>
+        <v>52307</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -4437,7 +4384,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 `entities/insert` accepts string numbers for Int64 primary key (type coercion gap; gRPC rejects)</t>
+          <t>[Bug]: entities/upsert JSON field — plain string overwrites valid JSON; written value unreadable via gRPC; REST/gRPC store inconsistent formats</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4455,7 +4402,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-07T14:25:31Z</t>
+          <t>2026-08-07T13:09:40Z</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4470,12 +4417,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>TP_DUP_TRACKED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4485,7 +4432,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>B 真 bug：重复，已在别处追踪</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4494,7 +4441,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="57">
@@ -4504,7 +4451,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52309</v>
+        <v>52308</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -4513,12 +4460,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 `entities/search` accepts `group_size=0` and `-1` (gRPC rejects as "negative")</t>
+          <t>[Bug]: REST API v2 `entities/insert` accepts string numbers for Int64 primary key (type coercion gap; gRPC rejects)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G57" t="b">
@@ -4526,7 +4478,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-08-07T14:28:01Z</t>
+          <t>2026-08-07T14:25:31Z</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4541,12 +4493,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_DUP_TRACKED</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4556,7 +4508,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：重复，已在别处追踪</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4575,7 +4527,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52310</v>
+        <v>52309</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4584,17 +4536,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 `entities/insert` silently coerces scalar types (string→Int64, int→VarChar, string→Bool); gRPC rejects all</t>
+          <t>[Bug]: REST API v2 `entities/search` accepts `group_size=0` and `-1` (gRPC rejects as "negative")</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G58" t="b">
@@ -4602,7 +4549,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-07T14:29:23Z</t>
+          <t>2026-08-07T14:28:01Z</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4617,12 +4564,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>TP_DUP_TRACKED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4632,16 +4579,16 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>B 真 bug：重复，已在别处追踪</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="59">
@@ -4651,7 +4598,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52311</v>
+        <v>52310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -4660,12 +4607,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 silently accepts `group_by_field` on vector fields (gRPC rejects "unsupported data type")</t>
+          <t>[Bug]: REST API v2 `entities/insert` silently coerces scalar types (string→Int64, int→VarChar, string→Bool); gRPC rejects all</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G59" t="b">
@@ -4673,7 +4625,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-08-07T14:30:36Z</t>
+          <t>2026-08-07T14:29:23Z</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4688,12 +4640,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_DUP_TRACKED</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4703,16 +4655,16 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：重复，已在别处追踪</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="60">
@@ -4722,7 +4674,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52312</v>
+        <v>52311</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -4731,17 +4683,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 `entities/upsert` accepts string numbers for Int64 primary key (gRPC rejects)</t>
+          <t>[Bug]: REST API v2 silently accepts `group_by_field` on vector fields (gRPC rejects "unsupported data type")</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G60" t="b">
@@ -4749,7 +4696,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-08-07T14:31:35Z</t>
+          <t>2026-08-07T14:30:36Z</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4764,12 +4711,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>TP_DUP_TRACKED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4779,12 +4726,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>B 真 bug：重复，已在别处追踪</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4798,7 +4745,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52313</v>
+        <v>52312</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -4807,12 +4754,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[Bug]: entities/insert JSON field — plain strings stored in inconsistent formats across REST/gRPC; written values unreadable via gRPC (round-trip failure)</t>
+          <t>[Bug]: REST API v2 `entities/upsert` accepts string numbers for Int64 primary key (gRPC rejects)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G61" t="b">
@@ -4820,7 +4772,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-08-07T14:33:10Z</t>
+          <t>2026-08-07T14:31:35Z</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4835,12 +4787,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_DUP_TRACKED</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4850,12 +4802,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：重复，已在别处追踪</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -4869,7 +4821,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52314</v>
+        <v>52313</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -4878,7 +4830,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 `entities/upsert` silently coerces scalar types (string→DOUBLE, string→BOOL, int→BOOL, string→INT16)</t>
+          <t>[Bug]: entities/insert JSON field — plain strings stored in inconsistent formats across REST/gRPC; written values unreadable via gRPC (round-trip failure)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4891,7 +4843,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-08-07T14:34:06Z</t>
+          <t>2026-08-07T14:33:10Z</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4906,12 +4858,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>TP_ACK_OPEN</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4921,7 +4873,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>B 真 bug：维护者确认但未修(open)</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4940,7 +4892,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>52315</v>
+        <v>52314</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -4949,7 +4901,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[Bug]: REST API v2 `entities/insert` accepts string-encoded vector values (gRPC rejects)</t>
+          <t>[Bug]: REST API v2 `entities/upsert` silently coerces scalar types (string→DOUBLE, string→BOOL, int→BOOL, string→INT16)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4962,7 +4914,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-08-07T14:35:11Z</t>
+          <t>2026-08-07T14:34:06Z</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4977,12 +4929,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4992,7 +4944,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>B 真 bug：维护者确认但未修(open)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5011,7 +4963,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>52325</v>
+        <v>52315</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -5020,7 +4972,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[Bug]: REST v2 entities/search silently ignores strictGroupSize</t>
+          <t>[Bug]: REST API v2 `entities/insert` accepts string-encoded vector values (gRPC rejects)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5033,7 +4985,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-08-08T13:38:45Z</t>
+          <t>2026-08-07T14:35:11Z</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5078,20 +5030,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>qdrant</t>
+          <t>milvus</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>8688</v>
+        <v>52325</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>qdrant/qdrant</t>
+          <t>milvus-io/milvus</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[Bug]: Cosine similarity score strictly exceeds upper bound of 1.0 for identical vectors</t>
+          <t>[Bug]: REST v2 entities/search silently ignores strictGroupSize</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5104,69 +5056,70 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-04-16T03:14:22Z</t>
+          <t>2026-08-08T13:38:45Z</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1.17.1</t>
+          <t>3.0.0</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>releases-api (latest &lt;= created_at)</t>
+          <t>(?i)milvus\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>qdrant</t>
+          <t>meilisearch</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>9017</v>
+        <v>6479</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>qdrant/qdrant</t>
+          <t>meilisearch/meilisearch</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>hnsw_ef accepts 0</t>
+          <t>Typo tolerance `minWordSizeForTypos` settings have no effect on search results</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G66" t="b">
@@ -5174,65 +5127,57 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-05-12T13:28:36Z</t>
+          <t>2026-06-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1.18.0</t>
+          <t>1.48.3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)meilisearch\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
-        </is>
-      </c>
-      <c r="P66" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自标（MEMBER ManyTheFish 已回应解释 prefix-search 行为，未裁决关闭）</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>qdrant</t>
+          <t>meilisearch</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>9027</v>
+        <v>6480</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>qdrant/qdrant</t>
+          <t>meilisearch/meilisearch</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>score_threshold_range_issue</t>
+          <t>Vector search returns 400 `missing_search_hybrid` despite `hybrid` documented as optional</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5242,7 +5187,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>not_planned</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="G67" t="b">
@@ -5250,22 +5195,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-05-13T04:50:14Z</t>
+          <t>2026-06-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1.18.0</t>
+          <t>1.48.3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)meilisearch\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5280,35 +5225,27 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P67" t="n">
-        <v>0.95</v>
+          <t>C 误报：维护者判定 by-design（MEMBER ManyTheFish：须显式指定 embedder，行为符合预期，文档无需修改；关闭 completed）</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>qdrant</t>
+          <t>meilisearch</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9039</v>
+        <v>6481</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>qdrant/qdrant</t>
+          <t>meilisearch/meilisearch</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bug: Async upsert silently discards dimension-mismatched vectors (Poor Diagnostics)</t>
+          <t>Embedder `dimensions=4097` accepted by settings API, exceeding documented maximum</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5326,46 +5263,38 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-05-14T00:54:32Z</t>
+          <t>2026-06-30T00:00:00Z</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1.18.0</t>
+          <t>1.48.3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)meilisearch\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P68" t="n">
-        <v>0.95</v>
+          <t>C 误报：维护者判定 by-design（dureuill：userProvided 源设计上不设维度上限，4096 文档依据不成立；关闭 completed）</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -5375,7 +5304,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>9044</v>
+        <v>8688</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -5384,7 +5313,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Collection creation accepts `size=65536` despite FAQ stating maximum is 65,535 (off-by-one)</t>
+          <t>[Bug]: Cosine similarity score strictly exceeds upper bound of 1.0 for identical vectors</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5397,17 +5326,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-05-14T12:54:58Z</t>
+          <t>2026-04-16T03:14:22Z</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1.12.1</t>
+          <t>1.17.1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>releases-api (latest &lt;= created_at)</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5430,8 +5359,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5440,7 +5367,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9045</v>
+        <v>9017</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -5449,7 +5376,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bug: Empty vector `[]` upsert with `wait=false` can trigger server panic (zero-length assertion failure)</t>
+          <t>hnsw_ef accepts 0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5467,17 +5394,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-05-14T12:58:57Z</t>
+          <t>2026-05-12T13:28:36Z</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1.12.1</t>
+          <t>1.18.0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -5502,7 +5429,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5516,7 +5443,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9149</v>
+        <v>9027</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -5525,7 +5452,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>shard_number=0 and negative values accepted during collection creation</t>
+          <t>score_threshold_range_issue</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5535,7 +5462,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>not_planned</t>
         </is>
       </c>
       <c r="G71" t="b">
@@ -5543,12 +5470,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-05-24T02:38:01Z</t>
+          <t>2026-05-13T04:50:14Z</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1.18.1</t>
+          <t>1.18.0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5558,27 +5485,27 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>C 误报：by-design(无 bug)</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
           <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5592,7 +5519,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>9255</v>
+        <v>9039</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5601,7 +5528,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Payload filter returns points with missing payload field (payload=None)</t>
+          <t>Bug: Async upsert silently discards dimension-mismatched vectors (Poor Diagnostics)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5619,46 +5546,46 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-06-01T12:21:26Z</t>
+          <t>2026-05-14T00:54:32Z</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1.18.1</t>
+          <t>1.18.0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>FP_NOT_REPRO</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>C 误报：不可复现</t>
+          <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="73">
@@ -5668,7 +5595,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9364</v>
+        <v>9044</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5677,17 +5604,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bug: Batch operations partially apply despite returning HTTP 400 error (atomicity violation)</t>
+          <t>Collection creation accepts `size=65536` despite FAQ stating maximum is 65,535 (off-by-one)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G73" t="b">
@@ -5695,22 +5617,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-06-08T11:52:05Z</t>
+          <t>2026-05-14T12:54:58Z</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1.18.2</t>
+          <t>1.12.1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])qdrant\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5725,11 +5647,9 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5738,7 +5658,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>9365</v>
+        <v>9045</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -5747,7 +5667,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bug: Payload index returns incorrect filtered results — index corruption after creation</t>
+          <t>Bug: Empty vector `[]` upsert with `wait=false` can trigger server panic (zero-length assertion failure)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5765,41 +5685,47 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-06-08T11:52:09Z</t>
+          <t>2026-05-14T12:58:57Z</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1.18.2</t>
+          <t>1.12.1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])qdrant\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5808,7 +5734,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9366</v>
+        <v>9149</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -5817,7 +5743,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Bug: Named vector lifecycle operations (update+delete) corrupt search — returns 400</t>
+          <t>shard_number=0 and negative values accepted during collection creation</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5835,41 +5761,47 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-06-08T11:52:14Z</t>
+          <t>2026-05-24T02:38:01Z</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1.18.2</t>
+          <t>1.18.1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])qdrant\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>FP_NOT_REPRO</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+          <t>C 误报:不可复现(phase3 终裁 DISPROVED 2026-08-17:qdrant v1.12.1~v1.18.2 共 7 版本全拒绝非法 shard_number,bug 从未存在;fix-PR #9178 实为补测试非修复)</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5878,7 +5810,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9371</v>
+        <v>9255</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -5887,12 +5819,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bug: Batch operations not atomic — valid points persisted despite HTTP 400 error</t>
+          <t>Payload filter returns points with missing payload field (payload=None)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G76" t="b">
@@ -5900,12 +5837,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-08T14:27:07Z</t>
+          <t>2026-06-01T12:21:26Z</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1.18.2</t>
+          <t>1.18.1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5915,7 +5852,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>FP_NOT_REPRO</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5930,7 +5867,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
+          <t>C 误报：不可复现</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5939,7 +5876,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="77">
@@ -5949,7 +5886,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>9372</v>
+        <v>9364</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -5958,12 +5895,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Strict mode inconsistently validates zero values — allows creation of unusable collections</t>
+          <t>Bug: Batch operations partially apply despite returning HTTP 400 error (atomicity violation)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G77" t="b">
@@ -5971,7 +5913,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-08T14:27:50Z</t>
+          <t>2026-06-08T11:52:05Z</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5986,7 +5928,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6001,11 +5943,9 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6014,7 +5954,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>9373</v>
+        <v>9365</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -6023,7 +5963,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bug: Payload index silently returns severely incomplete results — 2/25 matching points after wait:true</t>
+          <t>Bug: Payload index returns incorrect filtered results — index corruption after creation</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6041,7 +5981,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-08T14:28:25Z</t>
+          <t>2026-06-08T11:52:09Z</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6056,31 +5996,23 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>FP_NOT_REPRO</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>C 误报：不可复现</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
-        </is>
-      </c>
-      <c r="P78" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -6090,7 +6022,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>9416</v>
+        <v>9366</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6099,7 +6031,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`vectors={}` silently accepted during collection creation — produces unusable collection</t>
+          <t>Bug: Named vector lifecycle operations (update+delete) corrupt search — returns 400</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6117,7 +6049,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-10T14:30:08Z</t>
+          <t>2026-06-08T11:52:14Z</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6127,36 +6059,28 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])qdrant\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P79" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -6166,7 +6090,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>9417</v>
+        <v>9371</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6175,17 +6099,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Missing `vectors` field silently accepted during collection creation — produces unusable collection</t>
+          <t>Bug: Batch operations not atomic — valid points persisted despite HTTP 400 error</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G80" t="b">
@@ -6193,7 +6112,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-10T14:30:26Z</t>
+          <t>2026-06-08T14:27:07Z</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6208,7 +6127,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6223,7 +6142,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
+          <t>C 误报：by-design(无 bug)</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6242,7 +6161,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9418</v>
+        <v>9372</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6251,17 +6170,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`filter.should=null` silently accepted in query/search — null filter condition ignored</t>
+          <t>Strict mode inconsistently validates zero values — allows creation of unusable collections</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G81" t="b">
@@ -6269,7 +6183,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-10T14:30:42Z</t>
+          <t>2026-06-08T14:27:50Z</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6279,36 +6193,28 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])qdrant\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
-        </is>
-      </c>
-      <c r="P81" t="n">
-        <v>0.98</v>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -6318,7 +6224,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9419</v>
+        <v>9373</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6327,7 +6233,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`filter.must_not` accepts object instead of array — type mismatch silently ignored</t>
+          <t>Bug: Payload index silently returns severely incomplete results — 2/25 matching points after wait:true</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6345,7 +6251,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-10T14:30:57Z</t>
+          <t>2026-06-08T14:28:25Z</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6355,12 +6261,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])qdrant\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>FP_NOT_REPRO</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6375,12 +6281,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
+          <t>C 误报：不可复现</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6394,7 +6300,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>9420</v>
+        <v>9416</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -6403,7 +6309,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`query=null` silently accepted — returns all points instead of being rejected</t>
+          <t>`vectors={}` silently accepted during collection creation — produces unusable collection</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6421,7 +6327,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-06-10T14:31:15Z</t>
+          <t>2026-06-10T14:30:08Z</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6456,7 +6362,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6470,7 +6376,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>9421</v>
+        <v>9417</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -6479,12 +6385,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`POST /cluster/recover` returns HTTP 500 in standalone mode — should return 4xx</t>
+          <t>Missing `vectors` field silently accepted during collection creation — produces unusable collection</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G84" t="b">
@@ -6492,7 +6403,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-10T14:31:33Z</t>
+          <t>2026-06-10T14:30:26Z</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6507,22 +6418,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>C 误报：维护者判定 by-design</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6531,7 +6442,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="85">
@@ -6541,7 +6452,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>9520</v>
+        <v>9418</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -6550,12 +6461,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Server crash on collection creation with shard_number=INT_MAX — missing upper-bound validation unlike replication_factor</t>
+          <t>`filter.should=null` silently accepted in query/search — null filter condition ignored</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G85" t="b">
@@ -6563,7 +6479,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-06-20T02:18:26Z</t>
+          <t>2026-06-10T14:30:42Z</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6578,31 +6494,31 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>C 误报：维护者判定 by-design</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="86">
@@ -6612,7 +6528,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9521</v>
+        <v>9419</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -6621,12 +6537,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Silent data loss: named vector upsert in single-vector collection returns 200 OK but point is discarded</t>
+          <t>`filter.must_not` accepts object instead of array — type mismatch silently ignored</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G86" t="b">
@@ -6634,7 +6555,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-06-20T02:19:52Z</t>
+          <t>2026-06-10T14:30:57Z</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6649,26 +6570,32 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+          <t>C 误报：维护者判定 by-design</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6677,7 +6604,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9522</v>
+        <v>9420</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -6686,12 +6613,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Query API silently returns 200 OK when lookup_from references a non-existent collection</t>
+          <t>`query=null` silently accepted — returns all points instead of being rejected</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G87" t="b">
@@ -6699,7 +6631,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-06-20T02:32:25Z</t>
+          <t>2026-06-10T14:31:15Z</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6709,32 +6641,32 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>C 误报：维护者判定 by-design</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6748,7 +6680,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>9523</v>
+        <v>9421</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -6757,17 +6689,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Search offset pagination returns duplicate point IDs across pages (HNSW approximation)</t>
+          <t>`POST /cluster/recover` returns HTTP 500 in standalone mode — should return 4xx</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>not_planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G88" t="b">
@@ -6775,7 +6702,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-06-20T02:40:04Z</t>
+          <t>2026-06-10T14:31:33Z</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6785,36 +6712,36 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
           <t>FALSE_POSITIVE</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>C 误报：by-design(无 bug)</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
-        </is>
-      </c>
       <c r="P88" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="89">
@@ -6824,7 +6751,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9524</v>
+        <v>9520</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -6833,7 +6760,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Invalid filter conditions silently accepted (200 OK) with poor error diagnostics across search/query/scroll endpoints</t>
+          <t>Server crash on collection creation with shard_number=INT_MAX — missing upper-bound validation unlike replication_factor</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6846,7 +6773,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-06-20T02:41:40Z</t>
+          <t>2026-06-20T02:18:26Z</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6856,12 +6783,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>OPEN_NO_LABEL</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6876,11 +6803,17 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>D 未裁决：open 无标签</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者。【2026-08-30 错标纠正】原 A/TP_FIXED_PR 系误判：所依据的已合并 PR #9594 实为 CodeRabbit bot 在无关性能 PR（edge shard 并行加载）上的误交叉引用（"shard" 关键词撞车）。真实修复 PR #9526（Fixes #9520）2026-06-27 被关闭未合并；#10334（2026-08-25，AI-assisted）亦未合并；issue 仍 open，无成员回应。</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6889,7 +6822,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9525</v>
+        <v>9521</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -6898,7 +6831,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Systemic: serde deserialization errors across 7 endpoints expose Rust internal types (usize/u32/f32) and lack parameter names</t>
+          <t>Silent data loss: named vector upsert in single-vector collection returns 200 OK but point is discarded</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6911,7 +6844,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-06-20T03:12:50Z</t>
+          <t>2026-06-20T02:19:52Z</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6921,7 +6854,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6944,8 +6877,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6954,7 +6885,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9869</v>
+        <v>9522</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -6963,12 +6894,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Write operations accept `timeout=0` despite the OpenAPI schema declaring `minimum: 1`</t>
+          <t>Query API silently returns 200 OK when lookup_from references a non-existent collection</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>not_planned</t>
         </is>
       </c>
       <c r="G91" t="b">
@@ -6976,7 +6912,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-07-16T10:38:08Z</t>
+          <t>2026-06-20T02:32:25Z</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6991,26 +6927,32 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7019,7 +6961,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>9942</v>
+        <v>9523</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7028,12 +6970,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OpenAPI schema for `VectorParams.size` is missing the enforced `maximum: 65536` constraint</t>
+          <t>Search offset pagination returns duplicate point IDs across pages (HNSW approximation)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>not_planned</t>
         </is>
       </c>
       <c r="G92" t="b">
@@ -7041,7 +6988,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-07-23T03:55:38Z</t>
+          <t>2026-06-20T02:40:04Z</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7051,31 +6998,37 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
+          <t>C 误报：by-design(无 bug)</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7084,7 +7037,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>10120</v>
+        <v>9524</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7093,12 +7046,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`count` `exact=false` on `is_empty` under-counts ~35% consistently; `is_null` on the same field is correct</t>
+          <t>Invalid filter conditions silently accepted (200 OK) with poor error diagnostics across search/query/scroll endpoints</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G93" t="b">
@@ -7106,17 +7064,17 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-08-07T13:08:19Z</t>
+          <t>2026-06-20T02:41:40Z</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1.18.3</t>
+          <t>1.18.2</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -7138,14 +7096,6 @@
         <is>
           <t>A 真 bug：已被合并 PR 修复</t>
         </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P93" t="n">
-        <v>0.95</v>
       </c>
     </row>
     <row r="94">
@@ -7155,7 +7105,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>10124</v>
+        <v>9525</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7164,7 +7114,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`count` `exact=false` on numeric/datetime `range` filter returns bidirectionally-wrong counts (histogram estimator)</t>
+          <t>Systemic: serde deserialization errors across 7 endpoints expose Rust internal types (usize/u32/f32) and lack parameter names</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7177,17 +7127,17 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-08-07T14:26:22Z</t>
+          <t>2026-06-20T03:12:50Z</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1.18.3</t>
+          <t>1.18.2</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7210,8 +7160,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7220,7 +7168,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>10125</v>
+        <v>9869</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7229,7 +7177,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`count` `exact=false` on compound filter under-counts 20-60% when conditions touch the same field (independence assumption)</t>
+          <t>Write operations accept `timeout=0` despite the OpenAPI schema declaring `minimum: 1`</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7242,17 +7190,17 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-08-07T14:46:23Z</t>
+          <t>2026-07-16T10:38:08Z</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1.18.3</t>
+          <t>1.18.2</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -7275,8 +7223,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7285,7 +7231,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10126</v>
+        <v>9942</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7294,12 +7240,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`count` `exact=false` on `geo_radius` degenerates: medium radii collapse to a fixed value, large radii return the collection total</t>
+          <t>OpenAPI schema for `VectorParams.size` is missing the enforced `maximum: 65536` constraint</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G96" t="b">
@@ -7307,12 +7258,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-08-07T14:46:50Z</t>
+          <t>2026-07-23T03:55:38Z</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1.18.3</t>
+          <t>1.18.2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -7322,26 +7273,24 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复（MEMBER timvisee: implemented in #10324；2026-08-26 关闭 completed）</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7350,7 +7299,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>10127</v>
+        <v>10120</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -7359,7 +7308,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> `count` `exact=false` on `match_any` (multi-value) under-counts, increasingly with value count (independent-OR assumption)</t>
+          <t>`count` `exact=false` on `is_empty` under-counts ~35% consistently; `is_null` on the same field is correct</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7372,7 +7321,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-08-07T14:47:19Z</t>
+          <t>2026-08-07T13:08:19Z</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7387,54 +7336,55 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>11395</v>
+        <v>10124</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[Bug]: dynamicEfMin &gt; dynamicEfMax accepted during collection creation (no validation)</t>
+          <t>`count` `exact=false` on numeric/datetime `range` filter returns bidirectionally-wrong counts (histogram estimator)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G98" t="b">
@@ -7442,22 +7392,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-05-22T02:36:53Z</t>
+          <t>2026-08-07T14:26:22Z</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.18.3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7472,39 +7422,32 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>11396</v>
+        <v>10125</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[Bug]: flatSearchCutoff accepts negative values (no validation)</t>
+          <t>`count` `exact=false` on compound filter under-counts 20-60% when conditions touch the same field (independence assumption)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G99" t="b">
@@ -7512,69 +7455,62 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-05-22T02:36:54Z</t>
+          <t>2026-08-07T14:46:23Z</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.18.3</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者 | vendor accepted (label, 2026-08-30): team agrees count exact=false compound-filter under-count should be fixed</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>11397</v>
+        <v>10126</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[Bug]: replicationFactor=-1 accepted and silently normalized to 1 (no validation)</t>
+          <t>`count` `exact=false` on `geo_radius` degenerates: medium radii collapse to a fixed value, large radii return the collection total</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G100" t="b">
@@ -7582,69 +7518,62 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-05-22T02:36:56Z</t>
+          <t>2026-08-07T14:46:50Z</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.18.3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者 | vendor wontfix (closed not_planned by generall, 2026-08-30): 'An approximate count is allowed to be approximate' — geo_radius cardinality degeneracy declined</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>11398</v>
+        <v>10127</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[Bug]: bq.rescoreLimit=-1 accepted and silently discarded (no validation)</t>
+          <t xml:space="preserve"> `count` `exact=false` on `match_any` (multi-value) under-counts, increasingly with value count (independent-OR assumption)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G101" t="b">
@@ -7652,59 +7581,57 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-05-22T02:36:57Z</t>
+          <t>2026-08-07T14:47:19Z</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.18.3</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant/qdrant:v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者 | vendor accepted (label, 2026-08-30): count exact=false match_any (multi-value) under-count confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>11399</v>
+        <v>10368</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>dynamicEfMin &gt; dynamicEfMax accepted during collection creation (no validation)</t>
+          <t>Snapshot recovery with `priority: "replica"` silently destroys existing data</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7717,65 +7644,57 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-05-22T03:01:40Z</t>
+          <t>2026-08-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.19.0</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P102" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自标，待维护者（无回应） | vendor wontfix (closed not_planned by generall, 2026-08-30): snapshot recovery overwrite is by-design, priority=replica means replica is source of truth for sync (standalone: snapshot is only source); our chain audit independently concurs (NOT_DEFECT: behavior precisely restores snapshot state; recover.rs standalone branch does not consume priority)</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>11400</v>
+        <v>10369</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>flatSearchCutoff accepts negative values (no validation)</t>
+          <t>`recommend` bypasses vector dimension validation for `negative` examples from other collections</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7788,27 +7707,27 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-05-22T03:03:08Z</t>
+          <t>2026-08-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.19.0</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -7818,40 +7737,37 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P103" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自标，待维护者（外部 PR #10374 已挂未合并） | vendor accepted (label, 2026-08-30): recommend negative-example dimension bypass confirmed; community fix PR #10374 open</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>11401</v>
+        <v>10370</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>replicationFactor=-1 accepted and silently normalized to 1 (no validation)</t>
+          <t>`PATCH /collections/{c}` with `metadata: {}` does not remove metadata, contrary to versioned docs</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G104" t="b">
@@ -7859,65 +7775,57 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-05-22T03:04:25Z</t>
+          <t>2026-08-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.19.0</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>FP_BY_DESIGN</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P104" t="n">
-        <v>0.98</v>
+          <t>C 误报：维护者判定 by-design（qdrant-cloud-bot：文档已于 #9907 澄清 merge 语义，行为符合预期；关闭 completed。外部 PR #10379 未随关闭合并）</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>11402</v>
+        <v>10371</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>bq.rescoreLimit=-1 accepted and silently discarded (no validation)</t>
+          <t>`query/groups` without a query returns nondeterministic group members across identical requests</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7930,69 +7838,62 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-05-22T03:05:45Z</t>
+          <t>2026-08-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.19.0</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者（外部 PR #10378 已挂未合并） | vendor accepted (label, 2026-08-30): query/groups nondeterminism confirmed; community PR #10378 linked to close after merge</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>11433</v>
+        <v>10372</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[Schema Validation] Negative `ef` value (-1) accepted in vectorIndexConfig without validation error</t>
+          <t>`PUT /collections/{c}/index` accepts `field_schema` as a JSON array and creates wrong index</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G106" t="b">
@@ -8000,69 +7901,62 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-05-24T12:02:59Z</t>
+          <t>2026-08-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.19.0</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>SELF_CLOSED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自行关闭</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
+          <t>D 未裁决：报告者自标，待维护者（外部 PR #10377 已挂未合并） | vendor accepted (label, 2026-08-30): sequence field_schema acceptance confirmed; community PRs #10377/#10388 open</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>weaviate</t>
+          <t>qdrant</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>11436</v>
+        <v>10373</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>weaviate/weaviate</t>
+          <t>qdrant/qdrant</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Negative `ef` value (-1) accepted in vectorIndexConfig without validation error</t>
+          <t>`scroll` on a strict-mode collection ignores `max_query_limit` when `limit` is omitted</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>not_planned</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G107" t="b">
@@ -8070,46 +7964,38 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-05-24T13:56:10Z</t>
+          <t>2026-08-29T00:00:00Z</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1.37.4</t>
+          <t>1.19.0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)qdrant\s+version[:\s]*v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>BY_DESIGN</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>C 误报：by-design(无 bug)</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
-        </is>
-      </c>
-      <c r="P107" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自标，待维护者（无回应） | vendor fixed (label 'to be released', 2026-08-30): strict-mode limit materialization merged for next release</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -8119,7 +8005,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11660</v>
+        <v>11395</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -8128,12 +8014,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>REST API GET /v1/objects silently accepts negative limit parameter</t>
+          <t>[Bug]: dynamicEfMin &gt; dynamicEfMax accepted during collection creation (no validation)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G108" t="b">
@@ -8141,22 +8032,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-06-07T15:00:10Z</t>
+          <t>2026-05-22T02:36:53Z</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8171,11 +8062,9 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8184,7 +8073,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>11661</v>
+        <v>11396</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -8193,12 +8082,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>REST API GET /v1/objects returns HTTP 500 instead of 4xx when limit exceeds QUERY_MAXIMUM_RESULTS</t>
+          <t>[Bug]: flatSearchCutoff accepts negative values (no validation)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G109" t="b">
@@ -8206,22 +8100,22 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-06-07T15:01:10Z</t>
+          <t>2026-05-22T02:36:54Z</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8236,11 +8130,9 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8249,7 +8141,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>11729</v>
+        <v>11397</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -8258,7 +8150,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>shardingConfig.desiredCount accepts negative values but rejects zero</t>
+          <t>[Bug]: replicationFactor=-1 accepted and silently normalized to 1 (no validation)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8276,46 +8168,38 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-06-16T12:41:51Z</t>
+          <t>2026-05-22T02:36:56Z</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P110" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -8325,7 +8209,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>11730</v>
+        <v>11398</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -8334,12 +8218,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>tokenization accepts empty string despite explicit OpenAPI enum constraint</t>
+          <t>[Bug]: bq.rescoreLimit=-1 accepted and silently discarded (no validation)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G111" t="b">
@@ -8347,46 +8236,38 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-06-16T12:43:32Z</t>
+          <t>2026-05-22T02:36:57Z</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>CONFIRMED</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="P111" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -8396,7 +8277,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>11731</v>
+        <v>11399</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -8405,7 +8286,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>replicationConfig.deletionStrategy accepts empty string outside explicit OpenAPI enum</t>
+          <t>dynamicEfMin &gt; dynamicEfMax accepted during collection creation (no validation)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8418,41 +8299,47 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-06-16T12:44:49Z</t>
+          <t>2026-05-22T03:01:40Z</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+          <t>改判 2026-09-05:原标 TP_FIXED_PR 系错账——关联修复 PR 未 merge(closed-unmerged),用户确认知情范围内未修复;TP_ACK_OPEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8461,7 +8348,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>11732</v>
+        <v>11400</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -8470,7 +8357,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>vectorIndexConfig.distance silently accepts null and defaults to cosine</t>
+          <t>flatSearchCutoff accepts negative values (no validation)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8483,17 +8370,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-06-16T12:46:06Z</t>
+          <t>2026-05-22T03:03:08Z</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -8532,7 +8419,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>11734</v>
+        <v>11401</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -8541,7 +8428,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>multiTenancyConfig accepts null for boolean fields autoTenantCreation and autoTenantActivation</t>
+          <t>replicationFactor=-1 accepted and silently normalized to 1 (no validation)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8554,41 +8441,47 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-06-16T12:47:52Z</t>
+          <t>2026-05-22T03:04:25Z</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
+          <t>改判 2026-09-05:原标 TP_FIXED_PR 系错账——关联修复 PR 未 merge(closed-unmerged),用户确认知情范围内未修复;TP_ACK_OPEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8597,7 +8490,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>11735</v>
+        <v>11402</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -8606,7 +8499,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>int64 boundary value 9223372036854775807 silently truncated to 9223372036854776000</t>
+          <t>bq.rescoreLimit=-1 accepted and silently discarded (no validation)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8619,17 +8512,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-06-16T12:48:57Z</t>
+          <t>2026-05-22T03:05:45Z</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+          <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -8652,8 +8545,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8662,7 +8553,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>11736</v>
+        <v>11433</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -8671,12 +8562,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>blob accepts long non-base64 garbage string without validation</t>
+          <t>[Schema Validation] Negative `ef` value (-1) accepted in vectorIndexConfig without validation error</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G116" t="b">
@@ -8684,12 +8580,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-06-16T12:49:59Z</t>
+          <t>2026-05-24T12:02:59Z</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -8699,7 +8595,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>SELF_CLOSED</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8714,11 +8610,9 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+          <t>D 未裁决：报告者自行关闭</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8727,7 +8621,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>11737</v>
+        <v>11436</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -8736,12 +8630,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>date accepts year 0000 and pre-1970 values without proper RFC3339 validation</t>
+          <t>Negative `ef` value (-1) accepted in vectorIndexConfig without validation error</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>not_planned</t>
         </is>
       </c>
       <c r="G117" t="b">
@@ -8749,12 +8648,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-06-16T12:51:04Z</t>
+          <t>2026-05-24T13:56:10Z</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1.38.0</t>
+          <t>1.37.4</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -8764,26 +8663,32 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>BY_DESIGN</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>FALSE_POSITIVE</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
+          <t>C 误报：by-design(无 bug)</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8792,7 +8697,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>11738</v>
+        <v>11660</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -8801,7 +8706,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>phoneNumber.defaultCountry accepts invalid ISO 3166-1 alpha-2 code "ZZ"</t>
+          <t>REST API GET /v1/objects silently accepts negative limit parameter</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8814,7 +8719,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-06-16T12:52:09Z</t>
+          <t>2026-06-07T15:00:10Z</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8847,8 +8752,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8857,7 +8760,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>11739</v>
+        <v>11661</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -8866,7 +8769,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>phoneNumber.input accepts alphabetic characters like "CALL-NOW" without validation</t>
+          <t>REST API GET /v1/objects returns HTTP 500 instead of 4xx when limit exceeds QUERY_MAXIMUM_RESULTS</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8879,7 +8782,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-06-16T12:53:26Z</t>
+          <t>2026-06-07T15:01:10Z</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8912,8 +8815,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8922,7 +8823,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>11740</v>
+        <v>11729</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -8931,12 +8832,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GraphQL queries accept negative limit values</t>
+          <t>shardingConfig.desiredCount accepts negative values but rejects zero</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>completed</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -8944,7 +8850,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-06-16T12:54:34Z</t>
+          <t>2026-06-16T12:41:51Z</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8959,26 +8865,32 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_FIXED_PR</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
+          <t>A 真 bug：已被合并 PR 修复</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8987,7 +8899,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>11741</v>
+        <v>11730</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -8996,7 +8908,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Tenant creation accepts empty string for activityStatus</t>
+          <t>tokenization accepts empty string despite explicit OpenAPI enum constraint</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9009,7 +8921,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-06-16T13:02:02Z</t>
+          <t>2026-06-16T12:43:32Z</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9024,12 +8936,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>TP_FIXED_PR</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9039,7 +8951,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>A 真 bug：已被合并 PR 修复</t>
+          <t>改判 2026-09-05:原标 TP_FIXED_PR 系错账——关联修复 PR 未 merge(closed-unmerged),用户确认知情范围内未修复;TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9058,7 +8970,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>11742</v>
+        <v>11731</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -9067,7 +8979,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PQ bitCompression accepts string "true" instead of requiring boolean true</t>
+          <t>replicationConfig.deletionStrategy accepts empty string outside explicit OpenAPI enum</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9080,7 +8992,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-06-16T13:03:02Z</t>
+          <t>2026-06-16T12:44:49Z</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9113,8 +9025,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9123,7 +9033,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>11743</v>
+        <v>11732</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -9132,7 +9042,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>text property accepts strings containing NUL bytes (\x00) without validation</t>
+          <t>vectorIndexConfig.distance silently accepts null and defaults to cosine</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9145,7 +9055,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-06-16T13:04:00Z</t>
+          <t>2026-06-16T12:46:06Z</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9160,26 +9070,32 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>PENDING_SELF_LABELED</t>
+          <t>TP_ACK_OPEN</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>unadjudicated</t>
+          <t>CONFIRMED</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>D 未裁决：报告者自标，待维护者</t>
-        </is>
-      </c>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
+          <t>改判 2026-09-05:原标 TP_FIXED_PR 系错账——关联修复 PR 未 merge(closed-unmerged),用户确认知情范围内未修复;TP_ACK_OPEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9188,7 +9104,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>11744</v>
+        <v>11734</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -9197,7 +9113,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Text property accepts strings containing lone UTF-16 surrogates</t>
+          <t>multiTenancyConfig accepts null for boolean fields autoTenantCreation and autoTenantActivation</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9210,7 +9126,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-06-16T13:04:53Z</t>
+          <t>2026-06-16T12:47:52Z</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9243,8 +9159,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9253,7 +9167,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>11745</v>
+        <v>11735</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -9262,7 +9176,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Text property accepts strings containing ASCII control characters (SOH, STX, ETX)</t>
+          <t>int64 boundary value 9223372036854775807 silently truncated to 9223372036854776000</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9275,7 +9189,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-06-16T13:05:59Z</t>
+          <t>2026-06-16T12:48:57Z</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9308,8 +9222,6 @@
           <t>D 未裁决：报告者自标，待维护者</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9318,7 +9230,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>11981</v>
+        <v>11736</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -9327,17 +9239,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>POST /v1/batch/objects accepts empty vector `[]` and reports per-item SUCCESS (singular POST /v1/objects rejects with 422)</t>
+          <t>blob accepts long non-base64 garbage string without validation</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>completed</t>
+          <t>open</t>
         </is>
       </c>
       <c r="G126" t="b">
@@ -9345,12 +9252,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-07-05T06:05:48Z</t>
+          <t>2026-06-16T12:49:59Z</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1.38.2</t>
+          <t>1.38.0</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -9360,31 +9267,23 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>FP_BY_DESIGN</t>
+          <t>PENDING_SELF_LABELED</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>FALSE_POSITIVE</t>
+          <t>unadjudicated</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>C 误报：维护者判定 by-design</t>
-        </is>
-      </c>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>FALSE_POSITIVE</t>
-        </is>
-      </c>
-      <c r="P126" t="n">
-        <v>0.95</v>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -9394,72 +9293,723 @@
         </is>
       </c>
       <c r="B127" t="n">
+        <v>11737</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>date accepts year 0000 and pre-1970 values without proper RFC3339 validation</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G127" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-06-16T12:51:04Z</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>11738</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>phoneNumber.defaultCountry accepts invalid ISO 3166-1 alpha-2 code "ZZ"</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G128" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-06-16T12:52:09Z</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>11739</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>phoneNumber.input accepts alphabetic characters like "CALL-NOW" without validation</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G129" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-06-16T12:53:26Z</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>11740</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>GraphQL queries accept negative limit values</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-06-16T12:54:34Z</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>11741</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Tenant creation accepts empty string for activityStatus</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G131" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:02:02Z</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>TP_ACK_OPEN</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>改判 2026-09-05:原标 TP_FIXED_PR 系错账——关联修复 PR 未 merge(closed-unmerged),用户确认知情范围内未修复;TP_ACK_OPEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>11742</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PQ bitCompression accepts string "true" instead of requiring boolean true</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G132" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:03:02Z</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>11743</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>text property accepts strings containing NUL bytes (\x00) without validation</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G133" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:04:00Z</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>11744</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Text property accepts strings containing lone UTF-16 surrogates</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:04:53Z</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>11745</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Text property accepts strings containing ASCII control characters (SOH, STX, ETX)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G135" t="b">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-06-16T13:05:59Z</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1.38.0</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>PENDING_SELF_LABELED</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>unadjudicated</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>D 未裁决：报告者自标，待维护者</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>11981</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>weaviate/weaviate</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>POST /v1/batch/objects accepts empty vector `[]` and reports per-item SUCCESS (singular POST /v1/objects rejects with 422)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G136" t="b">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-07-05T06:05:48Z</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1.38.2</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>(?i)(?:semitechnologies/)?weaviate:v?(\d+\.\d+(?:\.\d+)?)</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>FP_BY_DESIGN</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>C 误报：维护者判定 by-design</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>FALSE_POSITIVE</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>weaviate</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
         <v>12041</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>weaviate/weaviate</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>Batch delete returns HTTP 500 instead of 422 when match.where or match.class is missing</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="G127" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" t="inlineStr">
+      <c r="G137" t="b">
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr">
         <is>
           <t>2026-07-07T12:05:16Z</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>1.38.2</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>(?i)(?&lt;![a-z])weaviate\s+v?(\d+\.\d+(?:\.\d+)?)</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>TP_FIXED_PR</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
+      <c r="N137" t="inlineStr">
         <is>
           <t>A 真 bug：已被合并 PR 修复</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
+      <c r="O137" t="inlineStr">
         <is>
           <t>FALSE_POSITIVE</t>
         </is>
       </c>
-      <c r="P127" t="n">
+      <c r="P137" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -9629,7 +10179,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -9704,7 +10254,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -9838,11 +10388,8 @@
           <t>合计 A∪B∪C (scored 用于指标)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -9851,11 +10398,8 @@
           <t>合计 D (unadjudicated)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
